--- a/volunteer_forms/009_volunteer_candidate_registration_form--volunteer_forms.xlsx
+++ b/volunteer_forms/009_volunteer_candidate_registration_form--volunteer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Emergency Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general',_'value':_'general'}</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'General', 'value': 'General'}</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'administrative',_'value':_'administrative'}</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Administrative', 'value': 'Administrative'}</t>
+          <t>Administrative</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'events',_'value':_'events'}</t>
+          <t>events</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Events', 'value': 'Events'}</t>
+          <t>Events</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'fundraising',_'value':_'fundraising'}</t>
+          <t>fundraising</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Fundraising', 'value': 'Fundraising'}</t>
+          <t>Fundraising</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one-time',_'value':_'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'One-time', 'value': 'One-time'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'ongoing',_'value':_'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Ongoing', 'value': 'Ongoing'}</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Weekly', 'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'bi-weekly',_'value':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Bi-Weekly', 'value': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Monthly', 'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-5_hours',_'value':_'1-5'}</t>
+          <t>1-5_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-5 hours', 'value': '1-5'}</t>
+          <t>1-5 hours</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'6-10_hours',_'value':_'6-10'}</t>
+          <t>6-10_hours</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '6-10 hours', 'value': '6-10'}</t>
+          <t>6-10 hours</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_10_hours',_'value':_'more_than_10'}</t>
+          <t>more_than_10_hours</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'More than 10 hours', 'value': 'More than 10'}</t>
+          <t>More than 10 hours</t>
         </is>
       </c>
     </row>
